--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Statistical_Validation/tables/top_evidence.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Statistical_Validation/tables/top_evidence.xlsx
@@ -534,26 +534,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>button_style_pref</t>
+          <t>mobile_sticky_header</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>65.66197244947071</v>
+        <v>14.5405572774308</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001286183419324869</v>
+        <v>0.04236106665679771</v>
       </c>
       <c r="F2" t="n">
-        <v>0.421868161538557</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05273352019231962</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H2" t="n">
-        <v>0.256245921820174</v>
+        <v>0.2547806941889191</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -573,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.8704897822446489</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001286183419324869</v>
+        <v>0.04236106665679771</v>
       </c>
     </row>
     <row r="3">
@@ -601,26 +601,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mobile_sticky_header</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12.48264731607355</v>
+        <v>68.50432172022388</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08576273356357941</v>
+        <v>0.0006037664252750105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.1980353874902034</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.02475442343627543</v>
       </c>
       <c r="H3" t="n">
-        <v>0.24982641289577</v>
+        <v>0.247314724520166</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -628,66 +628,66 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8430715509268312</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P3" t="b">
         <v>0</v>
       </c>
       <c r="Q3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08576273356357941</v>
+        <v>0.0006037664252750105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>desktop_search_visibility</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.86590646617123</v>
+        <v>12.18164420537235</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04755964831037239</v>
+        <v>0.03238184657806457</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2442637225734269</v>
+        <v>0.2332002148424292</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8489401726858951</v>
+        <v>0.8429996990577381</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -724,37 +724,37 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04755964831037239</v>
+        <v>0.03238184657806457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>button_style_pref</t>
+          <t>desktop_category_display</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.18817882088389</v>
+        <v>33.80211705015776</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01007289052385354</v>
+        <v>0.03804560723180549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4129885114779952</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2407705277898641</v>
+        <v>0.2242783302503334</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -774,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8655227202133037</v>
+        <v>0.8293622354354354</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01007289052385354</v>
+        <v>0.03804560723180549</v>
       </c>
     </row>
     <row r="6">
@@ -802,26 +802,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>desktop_persistent_filters</t>
+          <t>mobile_product_card</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.54028188024131</v>
+        <v>44.35431867020466</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1167269369347854</v>
+        <v>0.02562016680233264</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4703609319845312</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2402111766783689</v>
+        <v>0.2224917701883998</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -829,36 +829,36 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8093033727303587</v>
+        <v>0.8312914079845187</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Not Classified</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P6" t="b">
         <v>0</v>
       </c>
       <c r="Q6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1167269369347854</v>
+        <v>0.02562016680233264</v>
       </c>
     </row>
     <row r="7">
@@ -869,26 +869,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mobile_product_card</t>
+          <t>desktop_persistent_filters</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45.84472373991052</v>
+        <v>11.05632347668491</v>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01808408902555184</v>
+        <v>0.1361810175559039</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.7376416359031998</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3707238250238127</v>
+        <v>0.6203801910880065</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2393865173206046</v>
+        <v>0.2221679251140592</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8736398889490427</v>
+        <v>0.7345656585300209</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Not Classified</t>
         </is>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01808408902555184</v>
+        <v>0.1361810175559039</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>desktop_category_display</t>
+          <t>recommendation_type</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33.650420437344</v>
+        <v>32.1841524208596</v>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03948431736169739</v>
+        <v>0.006076529755922339</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.1673443007117269</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2368206791271404</v>
+        <v>0.2188448856144747</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8414788715893061</v>
+        <v>0.9146708149917904</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03948431736169739</v>
+        <v>0.006076529755922339</v>
       </c>
     </row>
     <row r="9">
@@ -1003,26 +1003,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>desktop_image_text_ratio</t>
+          <t>mobile_filter_location</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.42810448978032</v>
+        <v>21.4009937203421</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07023543703578852</v>
+        <v>0.091789215403546</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2367915987201632</v>
+        <v>0.2185636641087003</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8304975916476448</v>
+        <v>0.7683149515036278</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07023543703578852</v>
+        <v>0.091789215403546</v>
       </c>
     </row>
     <row r="10">
@@ -1070,26 +1070,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mobile_filter_location</t>
+          <t>desktop_search_visibility</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.82628163872918</v>
+        <v>21.28800831117746</v>
       </c>
       <c r="D10" t="n">
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08225498145138996</v>
+        <v>0.09447644303641907</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2335930309252032</v>
+        <v>0.2179859529753982</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1109,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8217800700514118</v>
+        <v>0.7665492064297157</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1126,37 +1126,37 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08225498145138996</v>
+        <v>0.09447644303641907</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Neuroticism_Level</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.52481747380307</v>
+        <v>21.27011268026897</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06165930323619846</v>
+        <v>0.01928683302746032</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.3953800770629365</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2293994057730215</v>
+        <v>0.2178943094481499</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1164,66 +1164,66 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7900144901512944</v>
+        <v>0.8389761699752223</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P11" t="b">
         <v>0</v>
       </c>
       <c r="Q11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.06165930323619846</v>
+        <v>0.01928683302746032</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>recommendation_type</t>
+          <t>social_proof_display</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31.39106946323544</v>
+        <v>10.56183481569735</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007784440760364039</v>
+        <v>0.03195580725403268</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1595810355874628</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2287322651166477</v>
+        <v>0.2171429213314659</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -1243,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9269018048245539</v>
+        <v>0.8206912347577575</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1260,37 +1260,37 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.007784440760364039</v>
+        <v>0.03195580725403268</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>button_style_pref</t>
+          <t>mobile_price_display</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.2980214084662</v>
+        <v>21.05260853833937</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06721813151455883</v>
+        <v>0.02072969480257041</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.2833058289684623</v>
       </c>
       <c r="H13" t="n">
-        <v>0.226914316521305</v>
+        <v>0.2167773737572234</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1298,66 +1298,66 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="b">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7845862594788657</v>
+        <v>0.8711345115542989</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P13" t="b">
         <v>0</v>
       </c>
       <c r="Q13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="b">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06721813151455883</v>
+        <v>0.02072969480257041</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mobile_sticky_header</t>
+          <t>desktop_image_text_ratio</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.04906946603638</v>
+        <v>20.81842396736526</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07385676408238892</v>
+        <v>0.1063769220277933</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6583326495304942</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6119327087415978</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2241547397004621</v>
+        <v>0.2155683101843265</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -1377,11 +1377,11 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.759088297650598</v>
+        <v>0.7589264485632992</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Not Classified</t>
         </is>
       </c>
       <c r="P14" t="b">
@@ -1391,40 +1391,40 @@
         <v>0</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07385676408238892</v>
+        <v>0.1063769220277933</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>desktop_price_display</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>40.19126297856479</v>
+        <v>10.20353848084781</v>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06357757297916758</v>
+        <v>0.0696692642803356</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.5148141803841989</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2241407564973537</v>
+        <v>0.2134279997451446</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8153011199927468</v>
+        <v>0.7782906838450014</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1461,37 +1461,37 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.06357757297916758</v>
+        <v>0.0696692642803356</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness_Level</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hero_banner_size</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.7058476100724</v>
+        <v>19.62573317382398</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09806027772742136</v>
+        <v>0.03299809885565442</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4467190429804751</v>
+        <v>0.6361436320471427</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2225078560788075</v>
+        <v>0.2093022697443647</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1499,66 +1499,66 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="b">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7985741736838935</v>
+        <v>0.7485265190253044</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P16" t="b">
         <v>0</v>
       </c>
       <c r="Q16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="b">
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.09806027772742136</v>
+        <v>0.03299809885565442</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness_Level</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>form_field_style</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>48.45276345166277</v>
+        <v>19.58054790334598</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003290526498034538</v>
+        <v>0.1439300752981853</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5396463456776642</v>
+        <v>0.7376416359031998</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1349115864194161</v>
+        <v>0.5709540419064413</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2201198842714187</v>
+        <v>0.2090611875537812</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1566,66 +1566,66 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9240659301618951</v>
+        <v>0.728568903278403</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Not Classified</t>
         </is>
       </c>
       <c r="P17" t="b">
         <v>0</v>
       </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.003290526498034538</v>
+        <v>0.1439300752981853</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Agreeableness_Level</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>button_style_pref</t>
+          <t>mobile_whitespace</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19.22358129100138</v>
+        <v>19.44250377428342</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03751305597841784</v>
+        <v>0.03498911993653327</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7192283768587451</v>
+        <v>0.358638479349466</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2192235234355644</v>
+        <v>0.2083229366266225</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7324510745960361</v>
+        <v>0.8312154939217499</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.03751305597841784</v>
+        <v>0.03498911993653327</v>
       </c>
     </row>
     <row r="19">
@@ -1673,26 +1673,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mobile_category_display</t>
+          <t>desktop_price_display</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19.19210488490492</v>
+        <v>38.61931088272131</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E19" t="n">
-        <v>0.157737928779403</v>
+        <v>0.08724306358434311</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6467255079955524</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G19" t="n">
-        <v>0.538937923329627</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2190439732388506</v>
+        <v>0.2076099936595608</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -1712,11 +1712,11 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7444088170823444</v>
+        <v>0.7546135426041427</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Not Classified</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P19" t="b">
@@ -1726,40 +1726,40 @@
         <v>0</v>
       </c>
       <c r="R19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.157737928779403</v>
+        <v>0.08724306358434311</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mobile_grid_pref</t>
+          <t>mobile_category_display</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.585975882803975</v>
+        <v>18.89846575433092</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02243409391836799</v>
+        <v>0.1688653048373149</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.7755751835748154</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.6771787167559145</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2189289369042381</v>
+        <v>0.205387622179353</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1767,66 +1767,66 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7894324882992878</v>
+        <v>0.6820961033534866</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Not Classified</t>
         </is>
       </c>
       <c r="P20" t="b">
         <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.02243409391836799</v>
+        <v>0.1688653048373149</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Extraversion_Level</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mobile_price_display</t>
+          <t>form_field_style</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>18.84612192927982</v>
+        <v>18.56922375445215</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0422612621360954</v>
+        <v>0.1820710034611609</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.7755751835748154</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5775705825266372</v>
+        <v>0.6220759284922999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2170606017295621</v>
+        <v>0.2035906681706896</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1834,66 +1834,66 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="b">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7709587881797708</v>
+        <v>0.6917084163889443</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Not Classified</t>
         </is>
       </c>
       <c r="P21" t="b">
         <v>0</v>
       </c>
       <c r="Q21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0422612621360954</v>
+        <v>0.1820710034611609</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Conscientiousness_Level</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_field_style</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18.43003569874318</v>
+        <v>45.09188072435776</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1878906798614224</v>
+        <v>0.008163136620084241</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6847571443838504</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4814698671448948</v>
+        <v>0.1673443007117269</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2146510872249613</v>
+        <v>0.2006504617228805</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1901,36 +1901,36 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7451069956533435</v>
+        <v>0.8884775696395767</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Not Classified</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P22" t="b">
         <v>0</v>
       </c>
       <c r="Q22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1878906798614224</v>
+        <v>0.008163136620084241</v>
       </c>
     </row>
     <row r="23">
@@ -1941,34 +1941,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>desktop_whitespace</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>36.67535265952063</v>
+        <v>17.08044264438286</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1261943963860937</v>
+        <v>0.2519164017560316</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.7970049787464639</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4703609319845312</v>
+        <v>0.6771787167559145</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2141125657788463</v>
+        <v>0.1952587720065284</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7696979220123458</v>
+        <v>0.6383307781658952</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1261943963860937</v>
+        <v>0.2519164017560316</v>
       </c>
     </row>
     <row r="24">
@@ -2008,34 +2008,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>desktop_persistent_filters</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17.56380493892523</v>
+        <v>8.499351138512278</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02474531586029017</v>
+        <v>0.01426886241579131</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5006317894422778</v>
+        <v>0.3953800770629365</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2095459671463831</v>
+        <v>0.1947909953472141</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -2047,24 +2047,24 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7902203425447025</v>
+        <v>0.8084484746312579</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P24" t="b">
         <v>0</v>
       </c>
       <c r="Q24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="b">
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.02474531586029017</v>
+        <v>0.01426886241579131</v>
       </c>
     </row>
     <row r="25">
@@ -2075,34 +2075,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>urgency_pref</t>
+          <t>hero_banner_size</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>34.921858282551</v>
+        <v>25.20849676419957</v>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1721534200167026</v>
+        <v>0.2382468919105295</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6722181162556958</v>
+        <v>0.7970049787464639</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5429454015911389</v>
+        <v>0.6771787167559145</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2089313831218009</v>
+        <v>0.1936818112119581</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7240168315415636</v>
+        <v>0.6409964874039809</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2131,74 +2131,74 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1721534200167026</v>
+        <v>0.2382468919105295</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Agreeableness_Level</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>desktop_navigation</t>
+          <t>form_field_style</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8.393373537164944</v>
+        <v>16.61992701658015</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>0.038544379976584</v>
+        <v>0.276998111633422</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.7970049787464639</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.9099813296804651</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2048581648014663</v>
+        <v>0.1926085444010597</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="b">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7641638402890324</v>
+        <v>0.5545719270151404</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Not Classified</t>
         </is>
       </c>
       <c r="P26" t="b">
         <v>0</v>
       </c>
       <c r="Q26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.038544379976584</v>
+        <v>0.276998111633422</v>
       </c>
     </row>
     <row r="27">
@@ -2209,34 +2209,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>checkout_style</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>41.68742528074741</v>
+        <v>32.99919661347629</v>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2027031908459282</v>
+        <v>0.2357740417875626</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7306224900820271</v>
+        <v>0.7970049787464639</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5936307731916469</v>
+        <v>0.6771787167559145</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2041749869125682</v>
+        <v>0.1919100323227317</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6910863698494289</v>
+        <v>0.63939946133488</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2265,45 +2265,45 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2027031908459282</v>
+        <v>0.2357740417875626</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>social_proof_display</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.327633523028096</v>
+        <v>41.22009127257017</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0802875452349027</v>
+        <v>0.2170643573014581</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.7970049787464639</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.6771787167559145</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2040543251566614</v>
+        <v>0.1918427817822126</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -2315,11 +2315,11 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7481959871679926</v>
+        <v>0.6459730945618222</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Not Classified</t>
         </is>
       </c>
       <c r="P28" t="b">
@@ -2329,48 +2329,48 @@
         <v>0</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0802875452349027</v>
+        <v>0.2170643573014581</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Conscientiousness_Level</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>accent_color_pref</t>
+          <t>mobile_navigation</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.28401235919791</v>
+        <v>24.61408578967892</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1785713221554904</v>
+        <v>0.2642648650754788</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6788878166662701</v>
+        <v>0.7970049787464639</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4814698671448948</v>
+        <v>0.6771787167559145</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2017672691444149</v>
+        <v>0.19138470120072</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7305339744600322</v>
+        <v>0.6285111762052094</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2399,57 +2399,57 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1785713221554904</v>
+        <v>0.2642648650754788</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Extraversion_Level</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>mobile_grid_pref</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.25633145468555</v>
+        <v>8.169479085881928</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09252597659675929</v>
+        <v>0.04263591033019484</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4584486025236872</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2015957058984984</v>
+        <v>0.1909735289935718</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.7679303378444348</v>
+        <v>0.7802804009117931</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2466,45 +2466,45 @@
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.09252597659675929</v>
+        <v>0.04263591033019484</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Conscientiousness_Level</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>mobile_price_display</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>16.14305813462319</v>
+        <v>16.28350690713988</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>0.09560977545161779</v>
+        <v>0.2963691985946416</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.81855620307043</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4814698671448948</v>
+        <v>0.6821301692253583</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2008921236299671</v>
+        <v>0.1906491899589627</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -2516,11 +2516,11 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.7588356505841873</v>
+        <v>0.6145286275560587</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Not Classified</t>
         </is>
       </c>
       <c r="P31" t="b">
@@ -2530,10 +2530,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.09560977545161779</v>
+        <v>0.2963691985946416</v>
       </c>
     </row>
   </sheetData>
@@ -2659,22 +2659,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>65.66197244947071</v>
+        <v>68.50432172022388</v>
       </c>
       <c r="D2" t="n">
         <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001286183419324869</v>
+        <v>0.0006037664252750105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.421868161538557</v>
+        <v>0.1980353874902034</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05273352019231962</v>
+        <v>0.02475442343627543</v>
       </c>
       <c r="H2" t="n">
-        <v>0.256245921820174</v>
+        <v>0.247314724520166</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -2711,7 +2711,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001286183419324869</v>
+        <v>0.0006037664252750105</v>
       </c>
     </row>
     <row r="3">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>31.39106946323544</v>
+        <v>32.1841524208596</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007784440760364039</v>
+        <v>0.006076529755922339</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1595810355874628</v>
+        <v>0.1673443007117269</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2287322651166477</v>
+        <v>0.2188448856144747</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9269018048245539</v>
+        <v>0.9146708149917904</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007784440760364039</v>
+        <v>0.006076529755922339</v>
       </c>
     </row>
     <row r="4">
@@ -2793,22 +2793,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48.45276345166277</v>
+        <v>45.09188072435776</v>
       </c>
       <c r="D4" t="n">
         <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003290526498034538</v>
+        <v>0.008163136620084241</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5396463456776642</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1349115864194161</v>
+        <v>0.1673443007117269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2201198842714187</v>
+        <v>0.2006504617228805</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9240659301618951</v>
+        <v>0.8884775696395767</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2845,37 +2845,37 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003290526498034538</v>
+        <v>0.008163136620084241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mobile_product_card</t>
+          <t>mobile_price_display</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.84472373991052</v>
+        <v>21.05260853833937</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01808408902555184</v>
+        <v>0.02072969480257041</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3707238250238127</v>
+        <v>0.2833058289684623</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2393865173206046</v>
+        <v>0.2167773737572234</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8736398889490427</v>
+        <v>0.8711345115542989</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2912,37 +2912,37 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01808408902555184</v>
+        <v>0.02072969480257041</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>button_style_pref</t>
+          <t>mobile_sticky_header</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.18817882088389</v>
+        <v>14.5405572774308</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01007289052385354</v>
+        <v>0.04236106665679771</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4129885114779952</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2407705277898641</v>
+        <v>0.2547806941889191</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8655227202133037</v>
+        <v>0.8704897822446489</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2979,37 +2979,37 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01007289052385354</v>
+        <v>0.04236106665679771</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>desktop_search_visibility</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.86590646617123</v>
+        <v>12.18164420537235</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04755964831037239</v>
+        <v>0.03238184657806457</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2442637225734269</v>
+        <v>0.2332002148424292</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8489401726858951</v>
+        <v>0.8429996990577381</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -3046,37 +3046,37 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04755964831037239</v>
+        <v>0.03238184657806457</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Neuroticism_Level</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mobile_sticky_header</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.48264731607355</v>
+        <v>21.27011268026897</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08576273356357941</v>
+        <v>0.01928683302746032</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.3953800770629365</v>
       </c>
       <c r="H8" t="n">
-        <v>0.24982641289577</v>
+        <v>0.2178943094481499</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3084,36 +3084,36 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8430715509268312</v>
+        <v>0.8389761699752223</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P8" t="b">
         <v>0</v>
       </c>
       <c r="Q8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08576273356357941</v>
+        <v>0.01928683302746032</v>
       </c>
     </row>
     <row r="9">
@@ -3124,26 +3124,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>desktop_category_display</t>
+          <t>mobile_product_card</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33.650420437344</v>
+        <v>44.35431867020466</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03948431736169739</v>
+        <v>0.02562016680233264</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2368206791271404</v>
+        <v>0.2224917701883998</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8414788715893061</v>
+        <v>0.8312914079845187</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -3180,37 +3180,37 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03948431736169739</v>
+        <v>0.02562016680233264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>desktop_image_text_ratio</t>
+          <t>mobile_whitespace</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.42810448978032</v>
+        <v>19.44250377428342</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07023543703578852</v>
+        <v>0.03498911993653327</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.358638479349466</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2367915987201632</v>
+        <v>0.2083229366266225</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3218,36 +3218,36 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="b">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8304975916476448</v>
+        <v>0.8312154939217499</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P10" t="b">
         <v>0</v>
       </c>
       <c r="Q10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.07023543703578852</v>
+        <v>0.03498911993653327</v>
       </c>
     </row>
     <row r="11">
@@ -3258,26 +3258,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mobile_filter_location</t>
+          <t>desktop_category_display</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.82628163872918</v>
+        <v>33.80211705015776</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08225498145138996</v>
+        <v>0.03804560723180549</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2335930309252032</v>
+        <v>0.2242783302503334</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3285,66 +3285,66 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8217800700514118</v>
+        <v>0.8293622354354354</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P11" t="b">
         <v>0</v>
       </c>
       <c r="Q11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08225498145138996</v>
+        <v>0.03804560723180549</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>desktop_price_display</t>
+          <t>social_proof_display</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40.19126297856479</v>
+        <v>10.56183481569735</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06357757297916758</v>
+        <v>0.03195580725403268</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2241407564973537</v>
+        <v>0.2171429213314659</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -3352,66 +3352,66 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="b">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8153011199927468</v>
+        <v>0.8206912347577575</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P12" t="b">
         <v>0</v>
       </c>
       <c r="Q12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="b">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.06357757297916758</v>
+        <v>0.03195580725403268</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Openness_Level</t>
+          <t>Neuroticism_Level</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mobile_category_display</t>
+          <t>desktop_persistent_filters</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13.74280265772146</v>
+        <v>8.499351138512278</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00816282292854476</v>
+        <v>0.01426886241579131</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3346757400703352</v>
+        <v>0.3953800770629365</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1853564313540365</v>
+        <v>0.1947909953472141</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -3431,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.813144112889837</v>
+        <v>0.8084484746312579</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -3448,61 +3448,61 @@
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.00816282292854476</v>
+        <v>0.01426886241579131</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness_Level</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>desktop_persistent_filters</t>
+          <t>mobile_whitespace</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11.54028188024131</v>
+        <v>13.70803696933256</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1167269369347854</v>
+        <v>0.008287613941412596</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4703609319845312</v>
+        <v>0.3397921715979164</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2402111766783689</v>
+        <v>0.1749236885231554</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="b">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8093033727303587</v>
+        <v>0.7997706793257575</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Not Classified</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P14" t="b">
@@ -3512,16 +3512,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1167269369347854</v>
+        <v>0.008287613941412596</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3530,42 +3530,42 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29.7058476100724</v>
+        <v>15.24606030978499</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09806027772742136</v>
+        <v>0.01842687334407999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4467190429804751</v>
+        <v>0.4043739620417602</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2225078560788075</v>
+        <v>0.1844759730156093</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="b">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7985741736838935</v>
+        <v>0.7897910920739846</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3582,45 +3582,45 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.09806027772742136</v>
+        <v>0.01842687334407999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>mobile_grid_pref</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.56380493892523</v>
+        <v>8.169479085881928</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02474531586029017</v>
+        <v>0.04263591033019484</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5006317894422778</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2095459671463831</v>
+        <v>0.1909735289935718</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -3632,24 +3632,24 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7902203425447025</v>
+        <v>0.7802804009117931</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P16" t="b">
         <v>0</v>
       </c>
       <c r="Q16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="b">
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.02474531586029017</v>
+        <v>0.04263591033019484</v>
       </c>
     </row>
     <row r="17">
@@ -3664,22 +3664,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10.52481747380307</v>
+        <v>10.20353848084781</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06165930323619846</v>
+        <v>0.0696692642803356</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.5148141803841989</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2293994057730215</v>
+        <v>0.2134279997451446</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7900144901512944</v>
+        <v>0.7782906838450014</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3716,45 +3716,45 @@
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0.06165930323619846</v>
+        <v>0.0696692642803356</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Extraversion_Level</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mobile_grid_pref</t>
+          <t>mobile_review_display</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.585975882803975</v>
+        <v>12.87108487837288</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02243409391836799</v>
+        <v>0.01192317964216519</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.4045693561035546</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2189289369042381</v>
+        <v>0.1694995580375933</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -3766,74 +3766,74 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7894324882992878</v>
+        <v>0.7711007668807367</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P18" t="b">
         <v>0</v>
       </c>
       <c r="Q18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="b">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.02243409391836799</v>
+        <v>0.01192317964216519</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Extraversion_Level</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>recommendation_type</t>
+          <t>mobile_filter_location</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14.83527353993628</v>
+        <v>21.4009937203421</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02157734490210973</v>
+        <v>0.091789215403546</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4423355704932495</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1925829272023891</v>
+        <v>0.2185636641087003</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.785572985639454</v>
+        <v>0.7683149515036278</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3850,37 +3850,37 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.02157734490210973</v>
+        <v>0.091789215403546</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>button_style_pref</t>
+          <t>desktop_search_visibility</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10.2980214084662</v>
+        <v>21.28800831117746</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06721813151455883</v>
+        <v>0.09447644303641907</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H20" t="n">
-        <v>0.226914316521305</v>
+        <v>0.2179859529753982</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7845862594788657</v>
+        <v>0.7665492064297157</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3917,37 +3917,37 @@
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.06721813151455883</v>
+        <v>0.09447644303641907</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Extraversion_Level</t>
+          <t>Neuroticism_Level</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mobile_review_display</t>
+          <t>mobile_navigation</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13.10410015024543</v>
+        <v>13.83226302974856</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01077818585613501</v>
+        <v>0.0315670455689609</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4419056201015353</v>
+        <v>0.4314162894424657</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1809979292025563</v>
+        <v>0.1757145045805111</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7734609471557843</v>
+        <v>0.7645925377321275</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3984,128 +3984,128 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.01077818585613501</v>
+        <v>0.0315670455689609</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mobile_price_display</t>
+          <t>mobile_product_card</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18.84612192927982</v>
+        <v>14.64066541203707</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0422612621360954</v>
+        <v>0.06652080313546443</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5775705825266372</v>
+        <v>0.4156720059720034</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2170606017295621</v>
+        <v>0.1807762615038186</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7709587881797708</v>
+        <v>0.7640253480660268</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P22" t="b">
         <v>0</v>
       </c>
       <c r="Q22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="b">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0422612621360954</v>
+        <v>0.06652080313546443</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Extraversion_Level</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>product_desc_length</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>36.67535265952063</v>
+        <v>13.05854568015153</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1261943963860937</v>
+        <v>0.04211560054246764</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4703609319845312</v>
+        <v>0.4045693561035546</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2141125657788463</v>
+        <v>0.1707294335040797</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="b">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7696979220123458</v>
+        <v>0.762061183782854</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Not Classified</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P23" t="b">
@@ -4115,40 +4115,40 @@
         <v>0</v>
       </c>
       <c r="R23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1261943963860937</v>
+        <v>0.04211560054246764</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Extraversion_Level</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>desktop_image_text_ratio</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.25633145468555</v>
+        <v>20.81842396736526</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09252597659675929</v>
+        <v>0.1063769220277933</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6583326495304942</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4584486025236872</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2015957058984984</v>
+        <v>0.2155683101843265</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -4168,11 +4168,11 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7679303378444348</v>
+        <v>0.7589264485632992</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Not Classified</t>
         </is>
       </c>
       <c r="P24" t="b">
@@ -4182,10 +4182,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.09252597659675929</v>
+        <v>0.1063769220277933</v>
       </c>
     </row>
     <row r="25">
@@ -4196,101 +4196,101 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mobile_product_card</t>
+          <t>checkout_style</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.05607182887269</v>
+        <v>14.26104427429195</v>
       </c>
       <c r="D25" t="n">
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04158454723497933</v>
+        <v>0.07521004644075296</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5135785999327165</v>
+        <v>0.4156720059720034</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2003501424311491</v>
+        <v>0.1784171743758398</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7675127603256419</v>
+        <v>0.7576289059283144</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P25" t="b">
         <v>0</v>
       </c>
       <c r="Q25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="b">
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.04158454723497933</v>
+        <v>0.07521004644075296</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>desktop_navigation</t>
+          <t>mobile_category_display</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8.393373537164944</v>
+        <v>11.70020776894192</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>0.038544379976584</v>
+        <v>0.0197255591239883</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.4043739620417602</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2048581648014663</v>
+        <v>0.161606111266038</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -4302,74 +4302,74 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7641638402890324</v>
+        <v>0.7573388296353425</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Moderate Statistical Evidence</t>
+          <t>Exploratory Evidence</t>
         </is>
       </c>
       <c r="P26" t="b">
         <v>0</v>
       </c>
       <c r="Q26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="b">
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.038544379976584</v>
+        <v>0.0197255591239883</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Extraversion_Level</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mobile_sticky_header</t>
+          <t>recommendation_type</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10.04906946603638</v>
+        <v>12.74073890201653</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07385676408238892</v>
+        <v>0.0473428383179138</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6211380387310291</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6119327087415978</v>
+        <v>0.4045693561035546</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2241547397004621</v>
+        <v>0.168639109742842</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="b">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.759088297650598</v>
+        <v>0.7572744560321533</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4386,37 +4386,37 @@
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.07385676408238892</v>
+        <v>0.0473428383179138</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Conscientiousness_Level</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>desktop_price_display</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.14305813462319</v>
+        <v>38.61931088272131</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09560977545161779</v>
+        <v>0.08724306358434311</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4814698671448948</v>
+        <v>0.5451817253924405</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2008921236299671</v>
+        <v>0.2076099936595608</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4436,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7588356505841873</v>
+        <v>0.7546135426041427</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4453,37 +4453,37 @@
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.09560977545161779</v>
+        <v>0.08724306358434311</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>Agreeableness_Level</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>social_proof_display</t>
+          <t>mobile_review_display</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14.95516295459562</v>
+        <v>12.97274309873333</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06002317400917948</v>
+        <v>0.01140974677560341</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5006317894422778</v>
+        <v>0.4677996177997398</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1933595288225772</v>
+        <v>0.1701676110350818</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4491,19 +4491,19 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7551945570894705</v>
+        <v>0.7529034949121673</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4520,37 +4520,37 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.06002317400917948</v>
+        <v>0.01140974677560341</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Extraversion_Level</t>
+          <t>Openness_Level</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>product_desc_length</t>
+          <t>urgency_pref</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12.46883564401741</v>
+        <v>13.83575937100729</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>0.05229061052089522</v>
+        <v>0.08614801146160327</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6351029189125033</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4496070433508397</v>
+        <v>0.4156720059720034</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1765561924998484</v>
+        <v>0.1757367106018013</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.7501754525434632</v>
+        <v>0.7499815424726431</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4587,37 +4587,37 @@
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.05229061052089522</v>
+        <v>0.08614801146160327</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Agreeableness_Level</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>social_proof_display</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8.327633523028096</v>
+        <v>19.62573317382398</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0802875452349027</v>
+        <v>0.03299809885565442</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.6361436320471427</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2040543251566614</v>
+        <v>0.2093022697443647</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4625,36 +4625,36 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
       </c>
       <c r="L31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.7481959871679926</v>
+        <v>0.7485265190253044</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Exploratory Evidence</t>
+          <t>Moderate Statistical Evidence</t>
         </is>
       </c>
       <c r="P31" t="b">
         <v>0</v>
       </c>
       <c r="Q31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="b">
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0802875452349027</v>
+        <v>0.03299809885565442</v>
       </c>
     </row>
   </sheetData>
